--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/2329-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/2329-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5C14E218-5CE6-4F13-A713-79DA2716FFC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{33740C7C-3C41-4B51-B594-F599ACACB980}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{181E2EFB-979C-4B8F-AC67-D079E63EF6C8}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{C90B9D71-EC2D-4B63-A5EE-A625D0B73E88}"/>
   </bookViews>
   <sheets>
     <sheet name="2329-dividend-20260225_0_4" sheetId="1" r:id="rId1"/>
@@ -1469,25 +1469,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C3A0017-897E-4772-9B2A-A732C511C13D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32B18D7E-FA98-46DD-950C-4B0C8DA0465C}">
   <dimension ref="A1:R52"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="2" width="7.33203125" customWidth="1"/>
-    <col min="3" max="3" width="8" customWidth="1"/>
-    <col min="4" max="4" width="8.33203125" customWidth="1"/>
-    <col min="5" max="5" width="8" customWidth="1"/>
-    <col min="6" max="7" width="8.33203125" customWidth="1"/>
-    <col min="8" max="9" width="8" customWidth="1"/>
-    <col min="10" max="10" width="8.33203125" customWidth="1"/>
-    <col min="11" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="8.33203125" customWidth="1"/>
-    <col min="15" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="9" customWidth="1"/>
+    <col min="1" max="1" width="6.5" customWidth="1"/>
+    <col min="2" max="2" width="9.25" customWidth="1"/>
+    <col min="3" max="3" width="10" customWidth="1"/>
+    <col min="4" max="4" width="10.5" customWidth="1"/>
+    <col min="5" max="5" width="10" customWidth="1"/>
+    <col min="6" max="7" width="10.5" customWidth="1"/>
+    <col min="8" max="9" width="10" customWidth="1"/>
+    <col min="10" max="10" width="10.5" customWidth="1"/>
+    <col min="11" max="13" width="10" customWidth="1"/>
+    <col min="14" max="14" width="10.5" customWidth="1"/>
+    <col min="15" max="17" width="10" customWidth="1"/>
+    <col min="18" max="18" width="10.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
@@ -1515,7 +1515,7 @@
       <c r="Q1" s="30"/>
       <c r="R1" s="22"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="23" t="s">
         <v>1</v>
       </c>
@@ -1545,7 +1545,7 @@
       <c r="Q2" s="32"/>
       <c r="R2" s="33"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="23" t="s">
         <v>2</v>
       </c>
@@ -1591,7 +1591,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="25"/>
       <c r="B4" s="26"/>
       <c r="C4" s="7"/>
@@ -1641,7 +1641,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="37">
         <v>2025</v>
       </c>
@@ -1695,7 +1695,7 @@
         <v>2.38</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="39">
         <v>2024</v>
       </c>
@@ -1749,7 +1749,7 @@
         <v>1.95</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="37">
         <v>2023</v>
       </c>
@@ -1803,7 +1803,7 @@
         <v>3.73</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
         <v>25</v>
       </c>
@@ -1859,7 +1859,7 @@
         <v>3.73</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
         <v>25</v>
       </c>
@@ -1915,7 +1915,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
         <v>25</v>
       </c>
@@ -1971,7 +1971,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="39">
         <v>2022</v>
       </c>
@@ -2025,7 +2025,7 @@
         <v>6.06</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="15" t="s">
         <v>25</v>
       </c>
@@ -2081,7 +2081,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="15" t="s">
         <v>25</v>
       </c>
@@ -2137,7 +2137,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="15" t="s">
         <v>25</v>
       </c>
@@ -2193,7 +2193,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="15" t="s">
         <v>25</v>
       </c>
@@ -2249,7 +2249,7 @@
         <v>6.06</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="37">
         <v>2021</v>
       </c>
@@ -2303,7 +2303,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
         <v>25</v>
       </c>
@@ -2359,7 +2359,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
         <v>25</v>
       </c>
@@ -2415,7 +2415,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
         <v>25</v>
       </c>
@@ -2471,7 +2471,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
         <v>25</v>
       </c>
@@ -2527,7 +2527,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="39">
         <v>2020</v>
       </c>
@@ -2581,7 +2581,7 @@
         <v>1.38</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="15" t="s">
         <v>25</v>
       </c>
@@ -2637,7 +2637,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="15" t="s">
         <v>25</v>
       </c>
@@ -2693,7 +2693,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="15" t="s">
         <v>25</v>
       </c>
@@ -2749,7 +2749,7 @@
         <v>1.38</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="37">
         <v>2019</v>
       </c>
@@ -2803,7 +2803,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="39">
         <v>2018</v>
       </c>
@@ -2857,7 +2857,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="37">
         <v>2017</v>
       </c>
@@ -2911,7 +2911,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="39">
         <v>2016</v>
       </c>
@@ -2965,7 +2965,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="37">
         <v>2015</v>
       </c>
@@ -3019,7 +3019,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="39">
         <v>2014</v>
       </c>
@@ -3073,7 +3073,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="37">
         <v>2013</v>
       </c>
@@ -3127,7 +3127,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="39">
         <v>2012</v>
       </c>
@@ -3181,7 +3181,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="37">
         <v>2011</v>
       </c>
@@ -3235,7 +3235,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="39">
         <v>2010</v>
       </c>
@@ -3289,7 +3289,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="37">
         <v>2009</v>
       </c>
@@ -3343,7 +3343,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A36" s="39">
         <v>2008</v>
       </c>
@@ -3397,7 +3397,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A37" s="37">
         <v>2007</v>
       </c>
@@ -3451,7 +3451,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A38" s="39">
         <v>2006</v>
       </c>
@@ -3505,7 +3505,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A39" s="37">
         <v>2005</v>
       </c>
@@ -3559,7 +3559,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A40" s="39">
         <v>2004</v>
       </c>
@@ -3613,7 +3613,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A41" s="37">
         <v>2003</v>
       </c>
@@ -3667,7 +3667,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A42" s="39">
         <v>2002</v>
       </c>
@@ -3721,7 +3721,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A43" s="37">
         <v>2001</v>
       </c>
@@ -3775,7 +3775,7 @@
         <v>11.3</v>
       </c>
     </row>
-    <row r="44" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A44" s="39">
         <v>2000</v>
       </c>
@@ -3829,7 +3829,7 @@
         <v>5.0999999999999996</v>
       </c>
     </row>
-    <row r="45" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A45" s="37">
         <v>1999</v>
       </c>
@@ -3883,7 +3883,7 @@
         <v>4.66</v>
       </c>
     </row>
-    <row r="46" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A46" s="39">
         <v>1998</v>
       </c>
@@ -3937,7 +3937,7 @@
         <v>7.98</v>
       </c>
     </row>
-    <row r="47" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A47" s="37">
         <v>1997</v>
       </c>
@@ -3991,7 +3991,7 @@
         <v>4.58</v>
       </c>
     </row>
-    <row r="48" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A48" s="39">
         <v>1996</v>
       </c>
@@ -4045,7 +4045,7 @@
         <v>9.65</v>
       </c>
     </row>
-    <row r="49" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A49" s="37">
         <v>1995</v>
       </c>
@@ -4099,7 +4099,7 @@
         <v>7.81</v>
       </c>
     </row>
-    <row r="50" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A50" s="39">
         <v>1994</v>
       </c>
@@ -4153,7 +4153,7 @@
         <v>2.44</v>
       </c>
     </row>
-    <row r="51" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A51" s="37">
         <v>1993</v>
       </c>
@@ -4207,7 +4207,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="52" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A52" s="39" t="s">
         <v>42</v>
       </c>
